--- a/artfynd/A 19260-2026 artfynd.xlsx
+++ b/artfynd/A 19260-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134441886</v>
+        <v>134441917</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508589</v>
+        <v>508538</v>
       </c>
       <c r="R2" t="n">
-        <v>6605561</v>
+        <v>6605550</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134441864</v>
+        <v>134441886</v>
       </c>
       <c r="B3" t="n">
-        <v>99105</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,35 +787,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508572</v>
+        <v>508589</v>
       </c>
       <c r="R3" t="n">
-        <v>6605528</v>
+        <v>6605561</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +863,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -890,27 +881,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134441810</v>
+        <v>134446884</v>
       </c>
       <c r="B4" t="n">
-        <v>58658</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -923,7 +914,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -933,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508578</v>
+        <v>508544</v>
       </c>
       <c r="R4" t="n">
-        <v>6605528</v>
+        <v>6605661</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1100,6 +1091,773 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134447048</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58563</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lilla Andsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>508536</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6605701</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134446893</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58260</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lilla Andsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>508520</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6605609</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134441805</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilla Andsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>508578</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6605528</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134441810</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lilla Andsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>508578</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6605528</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134446895</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lilla Andsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>508520</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6605609</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134267762</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lilla Andsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>508605</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6605595</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrskog, gran och tall</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134441864</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lilla Andsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>508572</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6605528</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19260-2026 artfynd.xlsx
+++ b/artfynd/A 19260-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134441917</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134441886</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446884</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134441901</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134447048</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446893</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134441805</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134441810</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446895</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134267762</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,8 +1912,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134441864</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>